--- a/tables.xlsx
+++ b/tables.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$616</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$616</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$619</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$619</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -85,7 +85,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00059669"/>
+        <fgColor rgb="001A7A5E"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J616"/>
+  <dimension ref="A1:J619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
+          <t>Rita Cecilia de la Hoz del Villar; Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="I497" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J497" s="4" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="I499" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J499" s="4" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="I591" s="4" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
+          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz; Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J591" s="4" t="inlineStr">
@@ -22191,12 +22191,12 @@
       </c>
       <c r="I601" s="4" t="inlineStr">
         <is>
-          <t>Graciela Victoria Franco Martinez</t>
+          <t>Graciela Victoria Franco Martinez; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J601" s="4" t="inlineStr">
         <is>
-          <t>Dirección de Humanidades</t>
+          <t>Dirección de Humanidades; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="I606" s="2" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Armando Antonio Mendoza Diaz; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J606" s="2" t="inlineStr">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="I607" s="4" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Jenifer Yoris Vasquez Aguilar; Armando Antonio Mendoza Diaz</t>
         </is>
       </c>
       <c r="J607" s="4" t="inlineStr">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="I609" s="4" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Armando Antonio Mendoza Diaz; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J609" s="4" t="inlineStr">
@@ -22515,12 +22515,12 @@
       </c>
       <c r="I610" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite</t>
+          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J610" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -22599,7 +22599,7 @@
     <row r="613" ht="16" customHeight="1">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105048960860</t>
+          <t>2-s2.0-105048895411</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
@@ -22623,19 +22623,19 @@
       </c>
       <c r="I613" s="4" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J613" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="614" ht="16" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105049556122</t>
+          <t>2-s2.0-105048935973</t>
         </is>
       </c>
       <c r="B614" s="3" t="n">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr"/>
@@ -22651,7 +22651,7 @@
       <c r="F614" s="2" t="inlineStr"/>
       <c r="G614" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H614" s="2" t="n">
@@ -22659,19 +22659,19 @@
       </c>
       <c r="I614" s="2" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J614" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="615" ht="16" customHeight="1">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105049607637</t>
+          <t>2-s2.0-105048955097</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr"/>
@@ -22687,7 +22687,7 @@
       <c r="F615" s="4" t="inlineStr"/>
       <c r="G615" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H615" s="4" t="n">
@@ -22695,19 +22695,19 @@
       </c>
       <c r="I615" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Jenifer Yoris Vasquez Aguilar</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J615" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="616" ht="16" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105049672910</t>
+          <t>2-s2.0-105048960860</t>
         </is>
       </c>
       <c r="B616" s="3" t="n">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr"/>
@@ -22723,25 +22723,133 @@
       <c r="F616" s="2" t="inlineStr"/>
       <c r="G616" s="2" t="inlineStr">
         <is>
+          <t>No Q</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>Cesar Augusto Viloria Nuñez; Mauro Antonio Gonzalez Sierra</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="16" customHeight="1">
+      <c r="A617" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105049672910</t>
+        </is>
+      </c>
+      <c r="B617" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D617" s="4" t="inlineStr"/>
+      <c r="E617" s="5" t="inlineStr"/>
+      <c r="F617" s="4" t="inlineStr"/>
+      <c r="G617" s="4" t="inlineStr">
+        <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H616" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="I616" s="2" t="inlineStr">
-        <is>
-          <t>Deyler Rafael Castilla Caballero</t>
-        </is>
-      </c>
-      <c r="J616" s="2" t="inlineStr">
+      <c r="H617" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I617" s="4" t="inlineStr">
+        <is>
+          <t>Deyler Rafael Castilla Caballero; Juan Gabriel Fajardo Cuadro</t>
+        </is>
+      </c>
+      <c r="J617" s="4" t="inlineStr">
         <is>
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
+    <row r="618" ht="16" customHeight="1">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105050225172</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C618" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr"/>
+      <c r="E618" s="3" t="inlineStr"/>
+      <c r="F618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>Jorgelina Cecilia Pasqualino</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="16" customHeight="1">
+      <c r="A619" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105050337604</t>
+        </is>
+      </c>
+      <c r="B619" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D619" s="4" t="inlineStr"/>
+      <c r="E619" s="5" t="inlineStr"/>
+      <c r="F619" s="4" t="inlineStr"/>
+      <c r="G619" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H619" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I619" s="4" t="inlineStr">
+        <is>
+          <t>Mary Judith Arias Tapia</t>
+        </is>
+      </c>
+      <c r="J619" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J616"/>
+  <autoFilter ref="A1:J619"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22752,7 +22860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J616"/>
+  <dimension ref="A1:J619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36512,7 +36620,7 @@
       <c r="H404" s="2" t="inlineStr"/>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
+          <t>Rita Cecilia de la Hoz del Villar; Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
@@ -39674,7 +39782,7 @@
       <c r="H497" s="4" t="inlineStr"/>
       <c r="I497" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J497" s="4" t="inlineStr">
@@ -39742,7 +39850,7 @@
       <c r="H499" s="4" t="inlineStr"/>
       <c r="I499" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J499" s="4" t="inlineStr">
@@ -39776,7 +39884,7 @@
       <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -42870,7 +42978,7 @@
       <c r="H591" s="4" t="inlineStr"/>
       <c r="I591" s="4" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
+          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz; Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J591" s="4" t="inlineStr">
@@ -43210,12 +43318,12 @@
       <c r="H601" s="4" t="inlineStr"/>
       <c r="I601" s="4" t="inlineStr">
         <is>
-          <t>Graciela Victoria Franco Martinez</t>
+          <t>Graciela Victoria Franco Martinez; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J601" s="4" t="inlineStr">
         <is>
-          <t>Dirección de Humanidades</t>
+          <t>Dirección de Humanidades; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
@@ -43380,7 +43488,7 @@
       <c r="H606" s="2" t="inlineStr"/>
       <c r="I606" s="2" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Armando Antonio Mendoza Diaz; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J606" s="2" t="inlineStr">
@@ -43414,7 +43522,7 @@
       <c r="H607" s="4" t="inlineStr"/>
       <c r="I607" s="4" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Jenifer Yoris Vasquez Aguilar; Armando Antonio Mendoza Diaz</t>
         </is>
       </c>
       <c r="J607" s="4" t="inlineStr">
@@ -43482,7 +43590,7 @@
       <c r="H609" s="4" t="inlineStr"/>
       <c r="I609" s="4" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Armando Antonio Mendoza Diaz; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J609" s="4" t="inlineStr">
@@ -43516,12 +43624,12 @@
       <c r="H610" s="2" t="inlineStr"/>
       <c r="I610" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite</t>
+          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J610" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -43596,7 +43704,7 @@
     <row r="613" ht="16" customHeight="1">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105048960860</t>
+          <t>2-s2.0-105048895411</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
@@ -43618,19 +43726,19 @@
       <c r="H613" s="4" t="inlineStr"/>
       <c r="I613" s="4" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J613" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="614" ht="16" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105049556122</t>
+          <t>2-s2.0-105048935973</t>
         </is>
       </c>
       <c r="B614" s="3" t="n">
@@ -43638,7 +43746,7 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr"/>
@@ -43646,25 +43754,25 @@
       <c r="F614" s="2" t="inlineStr"/>
       <c r="G614" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H614" s="2" t="inlineStr"/>
       <c r="I614" s="2" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J614" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="615" ht="16" customHeight="1">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105049607637</t>
+          <t>2-s2.0-105048955097</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -43672,7 +43780,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr"/>
@@ -43680,25 +43788,25 @@
       <c r="F615" s="4" t="inlineStr"/>
       <c r="G615" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H615" s="4" t="inlineStr"/>
       <c r="I615" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Jenifer Yoris Vasquez Aguilar</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J615" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="616" ht="16" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105049672910</t>
+          <t>2-s2.0-105048960860</t>
         </is>
       </c>
       <c r="B616" s="3" t="n">
@@ -43706,7 +43814,7 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr"/>
@@ -43714,23 +43822,125 @@
       <c r="F616" s="2" t="inlineStr"/>
       <c r="G616" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H616" s="2" t="inlineStr"/>
       <c r="I616" s="2" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Cesar Augusto Viloria Nuñez; Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="J616" s="2" t="inlineStr">
         <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="16" customHeight="1">
+      <c r="A617" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105049672910</t>
+        </is>
+      </c>
+      <c r="B617" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D617" s="4" t="inlineStr"/>
+      <c r="E617" s="5" t="inlineStr"/>
+      <c r="F617" s="4" t="inlineStr"/>
+      <c r="G617" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H617" s="4" t="inlineStr"/>
+      <c r="I617" s="4" t="inlineStr">
+        <is>
+          <t>Deyler Rafael Castilla Caballero; Juan Gabriel Fajardo Cuadro</t>
+        </is>
+      </c>
+      <c r="J617" s="4" t="inlineStr">
+        <is>
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
+    <row r="618" ht="16" customHeight="1">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105050225172</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C618" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr"/>
+      <c r="E618" s="3" t="inlineStr"/>
+      <c r="F618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr"/>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>Jorgelina Cecilia Pasqualino</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="16" customHeight="1">
+      <c r="A619" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105050337604</t>
+        </is>
+      </c>
+      <c r="B619" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D619" s="4" t="inlineStr"/>
+      <c r="E619" s="5" t="inlineStr"/>
+      <c r="F619" s="4" t="inlineStr"/>
+      <c r="G619" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H619" s="4" t="inlineStr"/>
+      <c r="I619" s="4" t="inlineStr">
+        <is>
+          <t>Mary Judith Arias Tapia</t>
+        </is>
+      </c>
+      <c r="J619" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J616"/>
+  <autoFilter ref="A1:J619"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44021,13 +44231,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>65</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>6</v>
@@ -44036,10 +44246,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>11</v>
@@ -44052,7 +44262,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -44352,13 +44562,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>65</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>6</v>
@@ -44495,13 +44705,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>9</v>
@@ -44510,10 +44720,10 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>22</v>
@@ -44522,11 +44732,11 @@
         <v>26</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -44540,13 +44750,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>2</v>
@@ -44558,7 +44768,7 @@
         <v>49</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>14</v>
@@ -44567,11 +44777,11 @@
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -44585,10 +44795,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -44603,7 +44813,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>22</v>
@@ -44616,7 +44826,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -44861,13 +45071,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>9</v>
@@ -44876,7 +45086,7 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>25</v>
@@ -44885,14 +45095,14 @@
         <v>37</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>55</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -44906,13 +45116,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>2</v>
@@ -44921,7 +45131,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>33</v>
@@ -44930,14 +45140,14 @@
         <v>34</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -44951,10 +45161,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -44966,7 +45176,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>18</v>
@@ -44982,7 +45192,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -45268,16 +45478,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0</v>
@@ -45290,7 +45500,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -45426,93 +45636,93 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>57210822856</t>
+          <t>57220927199</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>57210822856</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -45522,162 +45732,162 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>57220927199</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="J9" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>7005142049</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Lenny Alexandra Romero Perez</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>36142156300</t>
+          <t>7005142049</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>36142156300</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -45770,86 +45980,86 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>56581610900</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>56581610900</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$769</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$769</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$771</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$771</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J769"/>
+  <dimension ref="A1:J771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -27567,12 +27567,12 @@
       </c>
       <c r="I751" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J751" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
@@ -27819,7 +27819,7 @@
       </c>
       <c r="I758" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar</t>
+          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J758" s="2" t="inlineStr">
@@ -28224,8 +28224,80 @@
         </is>
       </c>
     </row>
+    <row r="770" ht="16" customHeight="1">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105051391635</t>
+        </is>
+      </c>
+      <c r="B770" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C770" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr"/>
+      <c r="E770" s="3" t="inlineStr"/>
+      <c r="F770" s="2" t="inlineStr"/>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="771" ht="16" customHeight="1">
+      <c r="A771" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105051711833</t>
+        </is>
+      </c>
+      <c r="B771" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C771" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D771" s="4" t="inlineStr"/>
+      <c r="E771" s="5" t="inlineStr"/>
+      <c r="F771" s="4" t="inlineStr"/>
+      <c r="G771" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H771" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I771" s="4" t="inlineStr">
+        <is>
+          <t>Harold Alberto Rodriguez Arias; Efraín Andrés Rodríguez Gasca</t>
+        </is>
+      </c>
+      <c r="J771" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J769"/>
+  <autoFilter ref="A1:J771"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28236,7 +28308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J769"/>
+  <dimension ref="A1:J771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53794,12 +53866,12 @@
       <c r="H751" s="4" t="inlineStr"/>
       <c r="I751" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J751" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
@@ -54032,7 +54104,7 @@
       <c r="H758" s="2" t="inlineStr"/>
       <c r="I758" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar</t>
+          <t>Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Jorge Luis Muñiz Olite; Jenifer Yoris Vasquez Aguilar; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J758" s="2" t="inlineStr">
@@ -54415,8 +54487,76 @@
         </is>
       </c>
     </row>
+    <row r="770" ht="16" customHeight="1">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105051391635</t>
+        </is>
+      </c>
+      <c r="B770" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C770" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr"/>
+      <c r="E770" s="3" t="inlineStr"/>
+      <c r="F770" s="2" t="inlineStr"/>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr"/>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="771" ht="16" customHeight="1">
+      <c r="A771" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105051711833</t>
+        </is>
+      </c>
+      <c r="B771" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C771" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D771" s="4" t="inlineStr"/>
+      <c r="E771" s="5" t="inlineStr"/>
+      <c r="F771" s="4" t="inlineStr"/>
+      <c r="G771" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H771" s="4" t="inlineStr"/>
+      <c r="I771" s="4" t="inlineStr">
+        <is>
+          <t>Harold Alberto Rodriguez Arias; Efraín Andrés Rodríguez Gasca</t>
+        </is>
+      </c>
+      <c r="J771" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J769"/>
+  <autoFilter ref="A1:J771"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54801,10 +54941,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>23</v>
@@ -54816,10 +54956,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>11</v>
@@ -54832,12 +54972,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -55226,10 +55366,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>23</v>
@@ -55241,10 +55381,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>9</v>
@@ -55257,12 +55397,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>84.1%</t>
         </is>
       </c>
     </row>
@@ -55369,13 +55509,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>12</v>
@@ -55384,7 +55524,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>42</v>
@@ -55396,11 +55536,11 @@
         <v>35</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -55414,10 +55554,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>147</v>
@@ -55432,7 +55572,7 @@
         <v>54</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>15</v>
@@ -55445,7 +55585,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -55735,13 +55875,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>12</v>
@@ -55750,7 +55890,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>39</v>
@@ -55759,14 +55899,14 @@
         <v>43</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>85</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -55780,10 +55920,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>147</v>
@@ -55798,7 +55938,7 @@
         <v>56</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>36</v>
@@ -55811,7 +55951,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -56228,7 +56368,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>6</v>
@@ -56246,7 +56386,7 @@
         <v>7</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
@@ -56300,86 +56440,86 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lenny Alexandra Romero Perez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>36142156300</t>
+          <t>57191333650</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E7" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>22</v>
-      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>57191333650</t>
+          <t>36142156300</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -6759,7 +6759,7 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Jose Luis Villa Ramirez; Sonia Helena Contreras Ortiz</t>
+          <t>Vilma Viviana Ojeda Caicedo; Cristina Osorio del Valle; Jose Luis Villa Ramirez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="I395" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz; Sonia Helena Contreras Ortiz</t>
+          <t>Cristina Osorio del Valle; Pedro Vazquez Miraz; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
@@ -16407,12 +16407,12 @@
       </c>
       <c r="I441" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
+          <t>Jose Luis Villa Ramirez; Cristina Osorio del Valle; Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J441" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -17631,12 +17631,12 @@
       </c>
       <c r="I475" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz; Lina Margarita Marrugo Salas; Juan Carlos Martinez Santos</t>
+          <t>Sonia Helena Contreras Ortiz; Cristina Osorio del Valle; Lina Margarita Marrugo Salas; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J475" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad; Escuela de Transf</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="I555" s="4" t="inlineStr">
         <is>
-          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
+          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Cristina Osorio del Valle; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="J555" s="4" t="inlineStr">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
+          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Cristina Osorio del Valle; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -21771,12 +21771,12 @@
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
+          <t>Jose Luis Villa Ramirez; Cristina Osorio del Valle; Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -34214,7 +34214,7 @@
       <c r="H173" s="4" t="inlineStr"/>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Jose Luis Villa Ramirez; Sonia Helena Contreras Ortiz</t>
+          <t>Vilma Viviana Ojeda Caicedo; Cristina Osorio del Valle; Jose Luis Villa Ramirez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -41762,12 +41762,12 @@
       <c r="H395" s="4" t="inlineStr"/>
       <c r="I395" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz; Sonia Helena Contreras Ortiz</t>
+          <t>Cristina Osorio del Valle; Pedro Vazquez Miraz; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
@@ -43326,12 +43326,12 @@
       <c r="H441" s="4" t="inlineStr"/>
       <c r="I441" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
+          <t>Jose Luis Villa Ramirez; Cristina Osorio del Valle; Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J441" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -44482,12 +44482,12 @@
       <c r="H475" s="4" t="inlineStr"/>
       <c r="I475" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz; Lina Margarita Marrugo Salas; Juan Carlos Martinez Santos</t>
+          <t>Sonia Helena Contreras Ortiz; Cristina Osorio del Valle; Lina Margarita Marrugo Salas; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J475" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad; Escuela de Transf</t>
         </is>
       </c>
     </row>
@@ -47202,7 +47202,7 @@
       <c r="H555" s="4" t="inlineStr"/>
       <c r="I555" s="4" t="inlineStr">
         <is>
-          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
+          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Cristina Osorio del Valle; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="J555" s="4" t="inlineStr">
@@ -47304,7 +47304,7 @@
       <c r="H558" s="2" t="inlineStr"/>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
+          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Cristina Osorio del Valle; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -48392,12 +48392,12 @@
       <c r="H590" s="2" t="inlineStr"/>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
+          <t>Jose Luis Villa Ramirez; Cristina Osorio del Valle; Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -55595,42 +55595,42 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>27</v>
-      </c>
       <c r="J4" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -55640,42 +55640,42 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="J5" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
@@ -55961,42 +55961,42 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -56006,42 +56006,42 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="J5" s="4" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
@@ -56440,86 +56440,86 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>57191333650</t>
+          <t>36142156300</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Lenny Alexandra Romero Perez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>36142156300</t>
+          <t>57191333650</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>38</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="H8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>22</v>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -56612,86 +56612,86 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>56581610900</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>56581610900</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -56913,86 +56913,86 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Edisson Chavarro Mesa</t>
+          <t>Jairo Francisco Useche Vivero</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>57188841051</t>
+          <t>24537991200</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>22</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Jairo Francisco Useche Vivero</t>
+          <t>Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>24537991200</t>
+          <t>57188841051</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -57042,7 +57042,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo</t>
+          <t>Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -57052,20 +57052,20 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>57220077867</t>
+          <t>57190688459</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
@@ -57074,7 +57074,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$771</definedName>
@@ -56149,7 +56149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -56612,129 +56612,129 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>56581610900</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>56581610900</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -57042,7 +57042,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Alberto Patiño Vanegas</t>
+          <t>Vilma Viviana Ojeda Caicedo</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -57052,20 +57052,20 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>57190688459</t>
+          <t>57220077867</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
@@ -57074,9 +57074,3105 @@
         <v>2</v>
       </c>
       <c r="J21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Alberto Patiño Vanegas</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>57190688459</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Jorgelina Cecilia Pasqualino</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>14622047600</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Alba Zulay Cardenas Escobar</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>57930948900</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Raul Andres Vargas Ramirez</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>57117284600</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Diaz Mendoza</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>55258973100</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Jenifer Yoris Vasquez Aguilar</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>57205400052</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Argemiro Palencia Diaz</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>56801043600</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Luis del Rio Cortina</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>57197807415</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Danilo Lusbin Ariza Rua</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>58618811100</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>57223851529</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Luis Villalba Acevedo</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>57918628600</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Lina Margarita Marrugo Salas</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>57392556500</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Armando Antonio Mendoza Diaz</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>57931099400</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Tania Lucia Cobos Cobos</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>57206773929</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>James Manuel Perez Moron</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>57322375300</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Oriana Susana Martinez Palomino</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>58620428800</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Hernando Rafael Altamar Mercado</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>57203321995</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Mauro Antonio Gonzalez Sierra</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>58803522300</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Adolfo Baltar Moreno</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>57216868622</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Mary Judith Arias Tapia</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>57219403758</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Acevedo Patiño</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>57197327858</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Deyler Rafael Castilla Caballero</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>57024211000</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Rita Cecilia de la Hoz del Villar</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>59326410200</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>58145499200</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Luis Muñiz Olite</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>57758796500</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>57350116000</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Maria Fernanda Medina Reyes</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>57221229836</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Cristina Osorio del Valle</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>57220068897</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Tania Isabel Jimenez Castilla</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>57204842254</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Luz Alejandra Magre Colorado</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>56682785300</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Yuranis Henriquez Nuñez</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>57982471000</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Rafael Payares Guevara</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>57219506381</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Veronica Tordecilla Acevedo</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>59326202000</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Harold Alberto Rodriguez Arias</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>57204847841</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Luis Alvis Arrieta</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>58068307100</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Eliecer Duque Pardo</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>57205658483</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Elias Rafael Geney Castro</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>57427876200</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>David Javier Fortich Perez</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>57201036449</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Humberto Manuel Marbello Peña</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>59325343900</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Toro Gonzalez</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>56380539800</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Miguel Abuchar Curi</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>58523557700</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Sergio Villar Salinas</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>57218294431</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Rafael David Mendez Anillo</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>57903699900</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Milton Cesar Guerrero Pajaro</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>57200615582</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>William Arellano Cartagena</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>58068069000</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Enrique Pereira Batista</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>57189892062</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>58917134900</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Jairo Humberto Cabrera Tovar</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>57193252278</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Efraín Andrés Rodríguez Gasca</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>57197028938</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Luis Ángel Porto Hernández</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>57804909800</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Yina Paola Cabarcas Mena</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>57421989500</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Eduardo Gomez Vasquez</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>57212006168</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Graciela Victoria Franco Martinez</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Dirección de Humanidades</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>60219600400</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Moises Ramon Quintana Alvarez</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>55783129400</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Iris Laudith Solano Cahuana</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>57219696066</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Martha Patricia Castro Porto</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>58928816700</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Armando Jose Mercado Vega</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>57824284000</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Mauro Antonio Maza Chamorro</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>55872162200</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Luz Marina Gómez Hernández</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>57215550013</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Lien Neil Tejeda López</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>60026192200</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Julio Antonio Gomez Mora</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>60514611700</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Fabian Alfonso Gazabon Arrieta</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>60514444200</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Isaac Zuñiga Silgado</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>60157655200</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Juan Camilo Medellin Rojas</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>60150905000</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Angela Patricia Barreto Maya</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>59269721500</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Stefania Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>59987226300</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Luis Carlos Diaz Canedo</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>57218297655</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Marelbi del Carmen Olmos Perez</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>58868256900</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Aarón Eduardo Espinosa Espinosa</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>58660078000</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Marcos Ricardo Posada Llorente</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>57222223605</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Misorly del Carmen Soto Acevedo</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>58523088300</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Gabriel Roman Melendez</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>56006978600</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$771</definedName>
@@ -56612,129 +56612,129 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>56581610900</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>56581610900</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E13" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -57042,7 +57042,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo</t>
+          <t>Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -57052,20 +57052,20 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>57220077867</t>
+          <t>57190688459</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
@@ -57074,7 +57074,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Alberto Patiño Vanegas</t>
+          <t>Vilma Viviana Ojeda Caicedo</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -57095,20 +57095,20 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>57190688459</t>
+          <t>57220077867</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0</v>
@@ -57117,7 +57117,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -57429,146 +57429,146 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Danilo Lusbin Ariza Rua</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>58618811100</t>
+          <t>57223851529</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>12</v>
       </c>
       <c r="E30" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Danilo Lusbin Ariza Rua</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>57223851529</t>
+          <t>58618811100</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis Villalba Acevedo</t>
+          <t>Armando Antonio Mendoza Diaz</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>57918628600</t>
+          <t>57931099400</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>57392556500</t>
+          <t>57918628600</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
@@ -57587,44 +57587,44 @@
         <v>0</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Armando Antonio Mendoza Diaz</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>57931099400</t>
+          <t>57392556500</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -57633,11 +57633,11 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -57687,7 +57687,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -57697,40 +57697,40 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>57322375300</t>
+          <t>58620428800</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -57740,33 +57740,33 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>58620428800</t>
+          <t>57322375300</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -57988,27 +57988,27 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>57024211000</t>
+          <t>57350116000</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>2</v>
@@ -58017,14 +58017,14 @@
         <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -58074,33 +58074,33 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>58145499200</t>
+          <t>57024211000</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>1</v>
@@ -58110,132 +58110,132 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis Muñiz Olite</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>57758796500</t>
+          <t>58145499200</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I46" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Jeovanny de Jesus Muentes Acevedo</t>
+          <t>Maria Fernanda Medina Reyes</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>57350116000</t>
+          <t>57221229836</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J47" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes</t>
+          <t>Cristina Osorio del Valle</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>57221229836</t>
+          <t>57220068897</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Cristina Osorio del Valle</t>
+          <t>Jorge Luis Muñiz Olite</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -58256,93 +58256,93 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>57220068897</t>
+          <t>57758796500</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E49" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4" t="n">
+      <c r="J49" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Yuranis Henriquez Nuñez</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>57204842254</t>
+          <t>57982471000</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Luz Alejandra Magre Colorado</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>56682785300</t>
+          <t>59326202000</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
@@ -58361,31 +58361,31 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez</t>
+          <t>Luz Alejandra Magre Colorado</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>57982471000</t>
+          <t>56682785300</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -58404,10 +58404,10 @@
         <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -58461,7 +58461,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -58471,20 +58471,20 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>59326202000</t>
+          <t>57204842254</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -58493,18 +58493,18 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Harold Alberto Rodriguez Arias</t>
+          <t>Jorge Eliecer Duque Pardo</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -58514,17 +58514,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>57204847841</t>
+          <t>57205658483</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>0</v>
@@ -58533,14 +58533,14 @@
         <v>0</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -58590,39 +58590,39 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Jorge Eliecer Duque Pardo</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>57205658483</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
@@ -58633,146 +58633,146 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>Harold Alberto Rodriguez Arias</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57204847841</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Enrique Pereira Batista</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>57201036449</t>
+          <t>57189892062</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña</t>
+          <t>Daniel Toro Gonzalez</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>59325343900</t>
+          <t>56380539800</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Daniel Toro Gonzalez</t>
+          <t>Milton Cesar Guerrero Pajaro</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>56380539800</t>
+          <t>57200615582</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
@@ -58782,10 +58782,10 @@
         <v>3</v>
       </c>
       <c r="F61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="H61" s="4" t="n">
         <v>0</v>
@@ -58794,41 +58794,41 @@
         <v>1</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Alfredo Miguel Abuchar Curi</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>58523557700</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>1</v>
@@ -58841,24 +58841,24 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Sergio Villar Salinas</t>
+          <t>William Arellano Cartagena</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>57218294431</t>
+          <t>58068069000</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
@@ -58868,23 +58868,23 @@
         <v>4</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -58934,7 +58934,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Milton Cesar Guerrero Pajaro</t>
+          <t>Sergio Villar Salinas</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -58944,57 +58944,57 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>57200615582</t>
+          <t>57218294431</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E65" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>William Arellano Cartagena</t>
+          <t>Humberto Manuel Marbello Peña</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>58068069000</t>
+          <t>59325343900</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>0</v>
@@ -59003,13 +59003,13 @@
         <v>1</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -59020,50 +59020,50 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Enrique Pereira Batista</t>
+          <t>Alfredo Miguel Abuchar Curi</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>57189892062</t>
+          <t>58523557700</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -59073,7 +59073,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>57804909800</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -59083,7 +59083,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>0</v>
@@ -59092,14 +59092,14 @@
         <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -59149,7 +59149,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Yina Paola Cabarcas Mena</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -59159,17 +59159,17 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>57197028938</t>
+          <t>57421989500</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>0</v>
@@ -59181,18 +59181,18 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -59202,17 +59202,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>57804909800</t>
+          <t>57197028938</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>0</v>
@@ -59224,7 +59224,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Yina Paola Cabarcas Mena</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -59245,17 +59245,17 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>57421989500</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0</v>
@@ -59264,38 +59264,38 @@
         <v>0</v>
       </c>
       <c r="I72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Gomez Vasquez</t>
+          <t>Moises Ramon Quintana Alvarez</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>57212006168</t>
+          <t>55783129400</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>0</v>
@@ -59307,14 +59307,14 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -59364,17 +59364,17 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Moises Ramon Quintana Alvarez</t>
+          <t>Mauro Antonio Maza Chamorro</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>55783129400</t>
+          <t>55872162200</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
@@ -59384,7 +59384,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>0</v>
@@ -59396,84 +59396,84 @@
         <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Iris Laudith Solano Cahuana</t>
+          <t>Eduardo Gomez Vasquez</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Centro de Idiomas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>57219696066</t>
+          <t>57212006168</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Martha Patricia Castro Porto</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>58928816700</t>
+          <t>57215550013</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>0</v>
@@ -59482,28 +59482,28 @@
         <v>0</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Armando Jose Mercado Vega</t>
+          <t>Iris Laudith Solano Cahuana</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Centro de Idiomas</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>57824284000</t>
+          <t>57219696066</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -59536,27 +59536,27 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Mauro Antonio Maza Chamorro</t>
+          <t>Martha Patricia Castro Porto</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>55872162200</t>
+          <t>58928816700</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>0</v>
@@ -59568,28 +59568,28 @@
         <v>0</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Armando Jose Mercado Vega</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>57215550013</t>
+          <t>57824284000</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -59602,10 +59602,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>0</v>
@@ -59622,17 +59622,17 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Lien Neil Tejeda López</t>
+          <t>Gabriel Roman Melendez</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>60026192200</t>
+          <t>56006978600</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
@@ -59648,10 +59648,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>0</v>
@@ -59665,24 +59665,24 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Julio Antonio Gomez Mora</t>
+          <t>Marcos Ricardo Posada Llorente</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>60514611700</t>
+          <t>57222223605</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -59694,38 +59694,38 @@
         <v>0</v>
       </c>
       <c r="I82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Fabian Alfonso Gazabon Arrieta</t>
+          <t>Luis Carlos Diaz Canedo</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>60514444200</t>
+          <t>57218297655</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
         <v>0</v>
@@ -59734,41 +59734,41 @@
         <v>0</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Isaac Zuñiga Silgado</t>
+          <t>Aarón Eduardo Espinosa Espinosa</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>60157655200</t>
+          <t>58660078000</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>0</v>
@@ -59780,38 +59780,38 @@
         <v>0</v>
       </c>
       <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Juan Camilo Medellin Rojas</t>
+          <t>Misorly del Carmen Soto Acevedo</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>60150905000</t>
+          <t>58523088300</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>0</v>
@@ -59820,17 +59820,17 @@
         <v>0</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -59880,27 +59880,27 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Stefania Arias Cifuentes</t>
+          <t>Marelbi del Carmen Olmos Perez</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Centro de Idiomas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>59987226300</t>
+          <t>58868256900</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4" t="n">
         <v>0</v>
@@ -59912,28 +59912,28 @@
         <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Luis Carlos Diaz Canedo</t>
+          <t>Stefania Arias Cifuentes</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Centro de Idiomas</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>57218297655</t>
+          <t>59987226300</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -59943,13 +59943,13 @@
         <v>1</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
@@ -59959,31 +59959,31 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Marelbi del Carmen Olmos Perez</t>
+          <t>Lien Neil Tejeda López</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>58868256900</t>
+          <t>60026192200</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="n">
         <v>0</v>
@@ -59992,41 +59992,41 @@
         <v>0</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Aarón Eduardo Espinosa Espinosa</t>
+          <t>Isaac Zuñiga Silgado</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>58660078000</t>
+          <t>60157655200</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>0</v>
@@ -60038,21 +60038,21 @@
         <v>0</v>
       </c>
       <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Marcos Ricardo Posada Llorente</t>
+          <t>Juan Camilo Medellin Rojas</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -60062,14 +60062,14 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>57222223605</t>
+          <t>60150905000</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>0</v>
@@ -60081,38 +60081,38 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Misorly del Carmen Soto Acevedo</t>
+          <t>Fabian Alfonso Gazabon Arrieta</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>58523088300</t>
+          <t>60514444200</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>0</v>
@@ -60121,41 +60121,41 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Roman Melendez</t>
+          <t>Julio Antonio Gomez Mora</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>56006978600</t>
+          <t>60514611700</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>0</v>
@@ -60167,14 +60167,14 @@
         <v>0</v>
       </c>
       <c r="I93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
